--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
@@ -3460,7 +3460,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T15:08:52.338Z</t>
+    <t>2026-10-02T15:30:07.248Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
@@ -3460,7 +3460,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T15:30:07.248Z</t>
+    <t>2026-10-02T16:18:52.286Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
@@ -3460,7 +3460,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T16:18:52.286Z</t>
+    <t>2026-10-02T19:28:14.704Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3193" uniqueCount="1118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3354" uniqueCount="1173">
   <si>
     <t>Key</t>
   </si>
@@ -149,7 +149,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Hotel booking release 2.0 (AQPI-32)</t>
+    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23)</t>
   </si>
   <si>
     <t>Carried over</t>
@@ -2495,6 +2495,138 @@
     <t>AQPI-36, REQ-132, BR-132</t>
   </si>
   <si>
+    <t>TC-F-134</t>
+  </si>
+  <si>
+    <t>A non-refundable booking cannot be cancelled free of charge</t>
+  </si>
+  <si>
+    <t>Verify a SAVER (prepaid, non-refundable) booking is refused and stays confirmed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book a SAVER rate
+2. Cancel the reservation</t>
+  </si>
+  <si>
+    <t>Cancel returns HTTP 409 NON_REFUNDABLE_RATE; the reservation is still CONFIRMED</t>
+  </si>
+  <si>
+    <t>AQPI-36, REQ-133, BR-133</t>
+  </si>
+  <si>
+    <t>TC-F-135</t>
+  </si>
+  <si>
+    <t>The confirmation of a flexible booking states free cancellation until 48 hours before check-in</t>
+  </si>
+  <si>
+    <t>Verify the confirmation e-mail of a refundable booking tells the guest when free cancellation closes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book a FLEX rate
+2. Open the confirmation e-mail</t>
+  </si>
+  <si>
+    <t>HTML and text parts say "Free cancellation until &lt;check-in minus 48 hours&gt; UTC (48 hours before check-in)."</t>
+  </si>
+  <si>
+    <t>AQPI-24, REQ-134, BR-134</t>
+  </si>
+  <si>
+    <t>TC-F-136</t>
+  </si>
+  <si>
+    <t>The confirmation of a non-refundable booking states no free-cancellation deadline</t>
+  </si>
+  <si>
+    <t>Verify a SAVER booking is not promised free cancellation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book a SAVER rate
+2. Open the confirmation e-mail</t>
+  </si>
+  <si>
+    <t>The confirmation e-mail carries no free-cancellation deadline</t>
+  </si>
+  <si>
+    <t>TC-F-137</t>
+  </si>
+  <si>
+    <t>Operations can retry a failed confirmation e-mail 3 times; retry 4 is refused</t>
+  </si>
+  <si>
+    <t>Verify at most 3 manual retries per failed message, so guests are not spammed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book with an address the provider rejects
+2. Retry the failed e-mail 4 times</t>
+  </si>
+  <si>
+    <t>First 3 retries HTTP 200, the next HTTP 409 RETRY_LIMIT_REACHED; the booking stays CONFIRMED</t>
+  </si>
+  <si>
+    <t>AQPI-25, REQ-135, BR-135</t>
+  </si>
+  <si>
+    <t>TC-F-138</t>
+  </si>
+  <si>
+    <t>A cancelled booking gets one cancellation e-mail, even when cancelled twice</t>
+  </si>
+  <si>
+    <t>Verify the guest is told about the cancellation exactly once, with a masked recipient for support.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book a FLEX rate
+2. Cancel the reservation
+3. Cancel it again
+4. List its messages as support</t>
+  </si>
+  <si>
+    <t>Both cancels HTTP 200 CANCELLED; exactly one CANCELLATION message, DELIVERED, recipient masked; the CONFIRMATION message is separate</t>
+  </si>
+  <si>
+    <t>AQPI-37, REQ-136, BR-136</t>
+  </si>
+  <si>
+    <t>TC-F-139</t>
+  </si>
+  <si>
+    <t>When the cancellation e-mail cannot be sent the booking stays cancelled</t>
+  </si>
+  <si>
+    <t>Verify e-mail failure is isolated from the cancellation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book a FLEX rate with an address the provider rejects
+2. Cancel the reservation
+3. View the reservation and its messages</t>
+  </si>
+  <si>
+    <t>selection.ratePlanCode=FLEX; guest.email=jane@fail.test; every other booking attribute from the hotel data dictionary examples</t>
+  </si>
+  <si>
+    <t>Cancel HTTP 200 CANCELLED; the reservation stays CANCELLED; the cancellation e-mail is recorded as FAILED</t>
+  </si>
+  <si>
+    <t>AQPI-37, REQ-137, BR-137</t>
+  </si>
+  <si>
+    <t>TC-F-140</t>
+  </si>
+  <si>
+    <t>Verify: Operational users see the cancellation e-mail with its own delivery state, separate from the confirmation</t>
+  </si>
+  <si>
+    <t>Confirm the behaviour "Operational users see the cancellation e-mail with its own delivery state, separate from the confirmation." (no executable template in the catalogue - manual verification).</t>
+  </si>
+  <si>
+    <t>Operational users see the cancellation e-mail with its own delivery state, separate from the confirmation.</t>
+  </si>
+  <si>
+    <t>AQPI-37, REQ-138, BR-138</t>
+  </si>
+  <si>
     <t>Data Set</t>
   </si>
   <si>
@@ -3436,6 +3568,49 @@
     <t>REQ-132</t>
   </si>
   <si>
+    <t>TD-F-134</t>
+  </si>
+  <si>
+    <t>REQ-133</t>
+  </si>
+  <si>
+    <t>TD-F-135</t>
+  </si>
+  <si>
+    <t>REQ-134</t>
+  </si>
+  <si>
+    <t>TD-F-136</t>
+  </si>
+  <si>
+    <t>TD-F-137</t>
+  </si>
+  <si>
+    <t>REQ-135</t>
+  </si>
+  <si>
+    <t>TD-F-138</t>
+  </si>
+  <si>
+    <t>REQ-136</t>
+  </si>
+  <si>
+    <t>TD-F-139</t>
+  </si>
+  <si>
+    <t>REQ-137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selection.ratePlanCode = FLEX
+guest.email = jane@fail.test</t>
+  </si>
+  <si>
+    <t>TD-F-140</t>
+  </si>
+  <si>
+    <t>REQ-138</t>
+  </si>
+  <si>
     <t>Field</t>
   </si>
   <si>
@@ -3448,7 +3623,7 @@
     <t>Agentic QE Platform - MVP</t>
   </si>
   <si>
-    <t>Hotel booking release 2.0 (AQPI-32) (CYC-4)</t>
+    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23) (CYC-4)</t>
   </si>
   <si>
     <t>Baseline</t>
@@ -3460,7 +3635,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T19:28:14.704Z</t>
+    <t>2026-10-02T19:44:35.503Z</t>
   </si>
   <si>
     <t>Column order</t>
@@ -3898,7 +4073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O138"/>
+  <dimension ref="A1:O145"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -10403,6 +10578,335 @@
         <v>29</v>
       </c>
     </row>
+    <row r="139" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="H139" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I139" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J139" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="K139" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="L139" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M139" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N139" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="O139" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="H140" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I140" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J140" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="K140" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="L140" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M140" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N140" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="O140" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="5" t="s">
+        <v>802</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="H141" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I141" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J141" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="K141" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="L141" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M141" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N141" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="O141" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="H142" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I142" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J142" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="K142" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="L142" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M142" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N142" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="O142" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="H143" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I143" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J143" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="K143" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="L143" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M143" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N143" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="O143" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="5" t="s">
+        <v>819</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="H144" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I144" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J144" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="K144" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="L144" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M144" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N144" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="O144" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="5" t="s">
+        <v>826</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>829</v>
+      </c>
+      <c r="H145" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I145" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J145" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="K145" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="L145" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M145" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N145" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="O145" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10413,7 +10917,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I138"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
@@ -10426,57 +10930,57 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>790</v>
+        <v>831</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>791</v>
+        <v>832</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>792</v>
+        <v>833</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>793</v>
+        <v>834</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>794</v>
+        <v>835</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>795</v>
+        <v>836</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>796</v>
+        <v>837</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>797</v>
+        <v>838</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>798</v>
+        <v>839</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>799</v>
+        <v>840</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I2" s="2">
         <v>1</v>
@@ -10484,28 +10988,28 @@
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>804</v>
+        <v>845</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>805</v>
+        <v>846</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I3" s="2">
         <v>1</v>
@@ -10513,28 +11017,28 @@
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>806</v>
+        <v>847</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
@@ -10542,28 +11046,28 @@
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>809</v>
+        <v>850</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
@@ -10571,28 +11075,28 @@
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>810</v>
+        <v>851</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>811</v>
+        <v>852</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -10600,28 +11104,28 @@
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>812</v>
+        <v>853</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>813</v>
+        <v>854</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -10629,28 +11133,28 @@
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>814</v>
+        <v>855</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>815</v>
+        <v>856</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>816</v>
+        <v>857</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>817</v>
+        <v>858</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I8" s="2">
         <v>1</v>
@@ -10658,28 +11162,28 @@
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>818</v>
+        <v>859</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>819</v>
+        <v>860</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I9" s="2">
         <v>1</v>
@@ -10687,28 +11191,28 @@
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>820</v>
+        <v>861</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>821</v>
+        <v>862</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>822</v>
+        <v>863</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>824</v>
+        <v>865</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>825</v>
+        <v>866</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I10" s="2">
         <v>1</v>
@@ -10716,28 +11220,28 @@
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>826</v>
+        <v>867</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>821</v>
+        <v>862</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>827</v>
+        <v>868</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>824</v>
+        <v>865</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>828</v>
+        <v>869</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I11" s="2">
         <v>1</v>
@@ -10745,28 +11249,28 @@
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>829</v>
+        <v>870</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>821</v>
+        <v>862</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>830</v>
+        <v>871</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>824</v>
+        <v>865</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>831</v>
+        <v>872</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I12" s="2">
         <v>1</v>
@@ -10774,28 +11278,28 @@
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>832</v>
+        <v>873</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>833</v>
+        <v>874</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I13" s="2">
         <v>1</v>
@@ -10803,28 +11307,28 @@
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>834</v>
+        <v>875</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>835</v>
+        <v>876</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I14" s="2">
         <v>1</v>
@@ -10832,28 +11336,28 @@
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>836</v>
+        <v>877</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>837</v>
+        <v>878</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I15" s="2">
         <v>1</v>
@@ -10861,28 +11365,28 @@
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>838</v>
+        <v>879</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>839</v>
+        <v>880</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I16" s="2">
         <v>1</v>
@@ -10890,28 +11394,28 @@
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>840</v>
+        <v>881</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>800</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I17" s="2">
         <v>1</v>
@@ -10919,28 +11423,28 @@
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>842</v>
+        <v>883</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>843</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="G18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>844</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>803</v>
       </c>
       <c r="I18" s="2">
         <v>1</v>
@@ -10948,28 +11452,28 @@
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>845</v>
+        <v>886</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>846</v>
+        <v>887</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I19" s="2">
         <v>1</v>
@@ -10977,28 +11481,28 @@
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>847</v>
+        <v>888</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>848</v>
+        <v>889</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I20" s="2">
         <v>1</v>
@@ -11006,28 +11510,28 @@
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>850</v>
+        <v>891</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I21" s="2">
         <v>1</v>
@@ -11035,28 +11539,28 @@
     </row>
     <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>851</v>
+        <v>892</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>852</v>
+        <v>893</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I22" s="2">
         <v>1</v>
@@ -11064,28 +11568,28 @@
     </row>
     <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>854</v>
+        <v>895</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I23" s="2">
         <v>1</v>
@@ -11093,28 +11597,28 @@
     </row>
     <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>855</v>
+        <v>896</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>856</v>
+        <v>897</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I24" s="2">
         <v>1</v>
@@ -11122,28 +11626,28 @@
     </row>
     <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>857</v>
+        <v>898</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>858</v>
+        <v>899</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I25" s="2">
         <v>1</v>
@@ -11151,28 +11655,28 @@
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>859</v>
+        <v>900</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>860</v>
+        <v>901</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>861</v>
+        <v>902</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I26" s="2">
         <v>1</v>
@@ -11180,28 +11684,28 @@
     </row>
     <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>862</v>
+        <v>903</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>863</v>
+        <v>904</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I27" s="2">
         <v>1</v>
@@ -11209,28 +11713,28 @@
     </row>
     <row r="28" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>864</v>
+        <v>905</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>179</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>865</v>
+        <v>906</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>866</v>
+        <v>907</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I28" s="2">
         <v>1</v>
@@ -11238,28 +11742,28 @@
     </row>
     <row r="29" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>867</v>
+        <v>908</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>868</v>
+        <v>909</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I29" s="2">
         <v>1</v>
@@ -11267,28 +11771,28 @@
     </row>
     <row r="30" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>869</v>
+        <v>910</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>870</v>
+        <v>911</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I30" s="2">
         <v>1</v>
@@ -11296,28 +11800,28 @@
     </row>
     <row r="31" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>871</v>
+        <v>912</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>198</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>870</v>
+        <v>911</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I31" s="2">
         <v>1</v>
@@ -11325,28 +11829,28 @@
     </row>
     <row r="32" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>872</v>
+        <v>913</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>203</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>873</v>
+        <v>914</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I32" s="2">
         <v>1</v>
@@ -11354,28 +11858,28 @@
     </row>
     <row r="33" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>874</v>
+        <v>915</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>208</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>875</v>
+        <v>916</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I33" s="2">
         <v>1</v>
@@ -11383,28 +11887,28 @@
     </row>
     <row r="34" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>876</v>
+        <v>917</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>214</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>877</v>
+        <v>918</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>866</v>
+        <v>907</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
@@ -11412,28 +11916,28 @@
     </row>
     <row r="35" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>878</v>
+        <v>919</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>220</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>879</v>
+        <v>920</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I35" s="2">
         <v>1</v>
@@ -11441,28 +11945,28 @@
     </row>
     <row r="36" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>880</v>
+        <v>921</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>881</v>
+        <v>922</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I36" s="2">
         <v>1</v>
@@ -11470,28 +11974,28 @@
     </row>
     <row r="37" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>882</v>
+        <v>923</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>883</v>
+        <v>924</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I37" s="2">
         <v>1</v>
@@ -11499,28 +12003,28 @@
     </row>
     <row r="38" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>884</v>
+        <v>925</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>236</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>885</v>
+        <v>926</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I38" s="2">
         <v>1</v>
@@ -11528,28 +12032,28 @@
     </row>
     <row r="39" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>886</v>
+        <v>927</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>241</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>887</v>
+        <v>928</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>866</v>
+        <v>907</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I39" s="2">
         <v>1</v>
@@ -11557,28 +12061,28 @@
     </row>
     <row r="40" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>888</v>
+        <v>929</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>247</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>889</v>
+        <v>930</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I40" s="2">
         <v>1</v>
@@ -11586,28 +12090,28 @@
     </row>
     <row r="41" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>890</v>
+        <v>931</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>891</v>
+        <v>932</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I41" s="2">
         <v>1</v>
@@ -11615,28 +12119,28 @@
     </row>
     <row r="42" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>892</v>
+        <v>933</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>258</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>893</v>
+        <v>934</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I42" s="2">
         <v>1</v>
@@ -11644,28 +12148,28 @@
     </row>
     <row r="43" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>894</v>
+        <v>935</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>263</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>895</v>
+        <v>936</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I43" s="2">
         <v>1</v>
@@ -11673,28 +12177,28 @@
     </row>
     <row r="44" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>896</v>
+        <v>937</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>268</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>897</v>
+        <v>938</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I44" s="2">
         <v>1</v>
@@ -11702,28 +12206,28 @@
     </row>
     <row r="45" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>898</v>
+        <v>939</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>273</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>899</v>
+        <v>940</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I45" s="2">
         <v>1</v>
@@ -11731,28 +12235,28 @@
     </row>
     <row r="46" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>900</v>
+        <v>941</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>278</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>901</v>
+        <v>942</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I46" s="2">
         <v>1</v>
@@ -11760,28 +12264,28 @@
     </row>
     <row r="47" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>902</v>
+        <v>943</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>284</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>903</v>
+        <v>944</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I47" s="2">
         <v>1</v>
@@ -11789,28 +12293,28 @@
     </row>
     <row r="48" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>904</v>
+        <v>945</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>286</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I48" s="2">
         <v>1</v>
@@ -11818,28 +12322,28 @@
     </row>
     <row r="49" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>906</v>
+        <v>947</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>291</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>907</v>
+        <v>948</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I49" s="2">
         <v>1</v>
@@ -11847,28 +12351,28 @@
     </row>
     <row r="50" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>908</v>
+        <v>949</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>297</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>909</v>
+        <v>950</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I50" s="2">
         <v>1</v>
@@ -11876,28 +12380,28 @@
     </row>
     <row r="51" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>910</v>
+        <v>951</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>303</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>911</v>
+        <v>952</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I51" s="2">
         <v>1</v>
@@ -11905,28 +12409,28 @@
     </row>
     <row r="52" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>912</v>
+        <v>953</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>913</v>
+        <v>954</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I52" s="2">
         <v>1</v>
@@ -11934,28 +12438,28 @@
     </row>
     <row r="53" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>914</v>
+        <v>955</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>314</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>915</v>
+        <v>956</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I53" s="2">
         <v>1</v>
@@ -11963,28 +12467,28 @@
     </row>
     <row r="54" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>916</v>
+        <v>957</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>319</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>917</v>
+        <v>958</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I54" s="2">
         <v>1</v>
@@ -11992,28 +12496,28 @@
     </row>
     <row r="55" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>918</v>
+        <v>959</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>324</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>919</v>
+        <v>960</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I55" s="2">
         <v>1</v>
@@ -12021,28 +12525,28 @@
     </row>
     <row r="56" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>920</v>
+        <v>961</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>329</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>921</v>
+        <v>962</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I56" s="2">
         <v>1</v>
@@ -12050,28 +12554,28 @@
     </row>
     <row r="57" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>922</v>
+        <v>963</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>334</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>923</v>
+        <v>964</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>924</v>
+        <v>965</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>817</v>
+        <v>858</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I57" s="2">
         <v>1</v>
@@ -12079,28 +12583,28 @@
     </row>
     <row r="58" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>925</v>
+        <v>966</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>341</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>926</v>
+        <v>967</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>927</v>
+        <v>968</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>817</v>
+        <v>858</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I58" s="2">
         <v>1</v>
@@ -12108,28 +12612,28 @@
     </row>
     <row r="59" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>928</v>
+        <v>969</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>348</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>929</v>
+        <v>970</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I59" s="2">
         <v>1</v>
@@ -12137,28 +12641,28 @@
     </row>
     <row r="60" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>930</v>
+        <v>971</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>353</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>931</v>
+        <v>972</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>927</v>
+        <v>968</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>817</v>
+        <v>858</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I60" s="2">
         <v>1</v>
@@ -12166,28 +12670,28 @@
     </row>
     <row r="61" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>932</v>
+        <v>973</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>359</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>933</v>
+        <v>974</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I61" s="2">
         <v>1</v>
@@ -12195,28 +12699,28 @@
     </row>
     <row r="62" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>934</v>
+        <v>975</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>364</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>935</v>
+        <v>976</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I62" s="2">
         <v>1</v>
@@ -12224,28 +12728,28 @@
     </row>
     <row r="63" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>936</v>
+        <v>977</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>369</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>937</v>
+        <v>978</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I63" s="2">
         <v>1</v>
@@ -12253,28 +12757,28 @@
     </row>
     <row r="64" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>938</v>
+        <v>979</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>374</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>939</v>
+        <v>980</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I64" s="2">
         <v>1</v>
@@ -12282,28 +12786,28 @@
     </row>
     <row r="65" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>940</v>
+        <v>981</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>379</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>941</v>
+        <v>982</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I65" s="2">
         <v>1</v>
@@ -12311,28 +12815,28 @@
     </row>
     <row r="66" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>942</v>
+        <v>983</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>384</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>943</v>
+        <v>984</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>944</v>
+        <v>985</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>824</v>
+        <v>865</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>945</v>
+        <v>986</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I66" s="2">
         <v>1</v>
@@ -12340,28 +12844,28 @@
     </row>
     <row r="67" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>946</v>
+        <v>987</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>391</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>947</v>
+        <v>988</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>948</v>
+        <v>989</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I67" s="2">
         <v>1</v>
@@ -12369,28 +12873,28 @@
     </row>
     <row r="68" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>949</v>
+        <v>990</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>398</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>950</v>
+        <v>991</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I68" s="2">
         <v>1</v>
@@ -12398,28 +12902,28 @@
     </row>
     <row r="69" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>951</v>
+        <v>992</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>403</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>952</v>
+        <v>993</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I69" s="2">
         <v>1</v>
@@ -12427,28 +12931,28 @@
     </row>
     <row r="70" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>953</v>
+        <v>994</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>408</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>954</v>
+        <v>995</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I70" s="2">
         <v>1</v>
@@ -12456,28 +12960,28 @@
     </row>
     <row r="71" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>955</v>
+        <v>996</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>414</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>956</v>
+        <v>997</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>957</v>
+        <v>998</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I71" s="2">
         <v>1</v>
@@ -12485,28 +12989,28 @@
     </row>
     <row r="72" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>958</v>
+        <v>999</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>421</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>956</v>
+        <v>997</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>959</v>
+        <v>1000</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I72" s="2">
         <v>1</v>
@@ -12514,28 +13018,28 @@
     </row>
     <row r="73" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>960</v>
+        <v>1001</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>427</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>961</v>
+        <v>1002</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I73" s="2">
         <v>1</v>
@@ -12543,28 +13047,28 @@
     </row>
     <row r="74" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>962</v>
+        <v>1003</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>432</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>963</v>
+        <v>1004</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>964</v>
+        <v>1005</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I74" s="2">
         <v>1</v>
@@ -12572,28 +13076,28 @@
     </row>
     <row r="75" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>965</v>
+        <v>1006</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>439</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>963</v>
+        <v>1004</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>966</v>
+        <v>1007</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I75" s="2">
         <v>1</v>
@@ -12601,28 +13105,28 @@
     </row>
     <row r="76" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>967</v>
+        <v>1008</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>445</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>963</v>
+        <v>1004</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>968</v>
+        <v>1009</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I76" s="2">
         <v>1</v>
@@ -12630,28 +13134,28 @@
     </row>
     <row r="77" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>969</v>
+        <v>1010</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>451</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>970</v>
+        <v>1011</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>971</v>
+        <v>1012</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>824</v>
+        <v>865</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>972</v>
+        <v>1013</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I77" s="2">
         <v>1</v>
@@ -12659,28 +13163,28 @@
     </row>
     <row r="78" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>973</v>
+        <v>1014</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>458</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>974</v>
+        <v>1015</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I78" s="2">
         <v>1</v>
@@ -12688,28 +13192,28 @@
     </row>
     <row r="79" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>463</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>976</v>
+        <v>1017</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I79" s="2">
         <v>1</v>
@@ -12717,28 +13221,28 @@
     </row>
     <row r="80" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>977</v>
+        <v>1018</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>468</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>978</v>
+        <v>1019</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I80" s="2">
         <v>1</v>
@@ -12746,28 +13250,28 @@
     </row>
     <row r="81" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>979</v>
+        <v>1020</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>474</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>980</v>
+        <v>1021</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I81" s="2">
         <v>1</v>
@@ -12775,28 +13279,28 @@
     </row>
     <row r="82" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>981</v>
+        <v>1022</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>480</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>982</v>
+        <v>1023</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I82" s="2">
         <v>1</v>
@@ -12804,28 +13308,28 @@
     </row>
     <row r="83" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>983</v>
+        <v>1024</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>486</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>984</v>
+        <v>1025</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I83" s="2">
         <v>1</v>
@@ -12833,28 +13337,28 @@
     </row>
     <row r="84" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>985</v>
+        <v>1026</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>491</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>986</v>
+        <v>1027</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I84" s="2">
         <v>1</v>
@@ -12862,28 +13366,28 @@
     </row>
     <row r="85" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>987</v>
+        <v>1028</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>496</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>988</v>
+        <v>1029</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I85" s="2">
         <v>1</v>
@@ -12891,28 +13395,28 @@
     </row>
     <row r="86" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>989</v>
+        <v>1030</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>501</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>990</v>
+        <v>1031</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>927</v>
+        <v>968</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>817</v>
+        <v>858</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I86" s="2">
         <v>1</v>
@@ -12920,28 +13424,28 @@
     </row>
     <row r="87" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>991</v>
+        <v>1032</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>507</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>992</v>
+        <v>1033</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>964</v>
+        <v>1005</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I87" s="2">
         <v>1</v>
@@ -12949,28 +13453,28 @@
     </row>
     <row r="88" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>993</v>
+        <v>1034</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>512</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>994</v>
+        <v>1035</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>966</v>
+        <v>1007</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I88" s="2">
         <v>1</v>
@@ -12978,28 +13482,28 @@
     </row>
     <row r="89" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>995</v>
+        <v>1036</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>518</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>996</v>
+        <v>1037</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I89" s="2">
         <v>1</v>
@@ -13007,28 +13511,28 @@
     </row>
     <row r="90" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>997</v>
+        <v>1038</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>524</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>998</v>
+        <v>1039</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I90" s="2">
         <v>1</v>
@@ -13036,28 +13540,28 @@
     </row>
     <row r="91" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>999</v>
+        <v>1040</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>526</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>1000</v>
+        <v>1041</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I91" s="2">
         <v>1</v>
@@ -13065,28 +13569,28 @@
     </row>
     <row r="92" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>1001</v>
+        <v>1042</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>531</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>1002</v>
+        <v>1043</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I92" s="2">
         <v>1</v>
@@ -13094,28 +13598,28 @@
     </row>
     <row r="93" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>1003</v>
+        <v>1044</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>533</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>1004</v>
+        <v>1045</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I93" s="2">
         <v>1</v>
@@ -13123,28 +13627,28 @@
     </row>
     <row r="94" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>1005</v>
+        <v>1046</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>538</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>1006</v>
+        <v>1047</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>1007</v>
+        <v>1048</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I94" s="2">
         <v>1</v>
@@ -13152,28 +13656,28 @@
     </row>
     <row r="95" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>1008</v>
+        <v>1049</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>545</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>1009</v>
+        <v>1050</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I95" s="2">
         <v>1</v>
@@ -13181,28 +13685,28 @@
     </row>
     <row r="96" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>1010</v>
+        <v>1051</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>550</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>1011</v>
+        <v>1052</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I96" s="2">
         <v>1</v>
@@ -13210,28 +13714,28 @@
     </row>
     <row r="97" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>1012</v>
+        <v>1053</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>555</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>1013</v>
+        <v>1054</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I97" s="2">
         <v>1</v>
@@ -13239,28 +13743,28 @@
     </row>
     <row r="98" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>1014</v>
+        <v>1055</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>560</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>1015</v>
+        <v>1056</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I98" s="2">
         <v>1</v>
@@ -13268,28 +13772,28 @@
     </row>
     <row r="99" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>1016</v>
+        <v>1057</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>566</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>1017</v>
+        <v>1058</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I99" s="2">
         <v>1</v>
@@ -13297,28 +13801,28 @@
     </row>
     <row r="100" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>1018</v>
+        <v>1059</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>571</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>1019</v>
+        <v>1060</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I100" s="2">
         <v>1</v>
@@ -13326,28 +13830,28 @@
     </row>
     <row r="101" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>1020</v>
+        <v>1061</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>576</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>1021</v>
+        <v>1062</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I101" s="2">
         <v>1</v>
@@ -13355,28 +13859,28 @@
     </row>
     <row r="102" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>1022</v>
+        <v>1063</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>581</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>1023</v>
+        <v>1064</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I102" s="2">
         <v>1</v>
@@ -13384,28 +13888,28 @@
     </row>
     <row r="103" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>1024</v>
+        <v>1065</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>586</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>1025</v>
+        <v>1066</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I103" s="2">
         <v>1</v>
@@ -13413,28 +13917,28 @@
     </row>
     <row r="104" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>1026</v>
+        <v>1067</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>591</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>1027</v>
+        <v>1068</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I104" s="2">
         <v>1</v>
@@ -13442,28 +13946,28 @@
     </row>
     <row r="105" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>1028</v>
+        <v>1069</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>593</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>1029</v>
+        <v>1070</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I105" s="2">
         <v>1</v>
@@ -13471,28 +13975,28 @@
     </row>
     <row r="106" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>1030</v>
+        <v>1071</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1031</v>
+        <v>1072</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I106" s="2">
         <v>1</v>
@@ -13500,28 +14004,28 @@
     </row>
     <row r="107" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>1032</v>
+        <v>1073</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>604</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>1033</v>
+        <v>1074</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I107" s="2">
         <v>1</v>
@@ -13529,28 +14033,28 @@
     </row>
     <row r="108" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>1034</v>
+        <v>1075</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>609</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>1035</v>
+        <v>1076</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I108" s="2">
         <v>1</v>
@@ -13558,28 +14062,28 @@
     </row>
     <row r="109" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>1036</v>
+        <v>1077</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>614</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>1037</v>
+        <v>1078</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I109" s="2">
         <v>1</v>
@@ -13587,28 +14091,28 @@
     </row>
     <row r="110" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>1038</v>
+        <v>1079</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>619</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>1039</v>
+        <v>1080</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I110" s="2">
         <v>1</v>
@@ -13616,28 +14120,28 @@
     </row>
     <row r="111" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>1040</v>
+        <v>1081</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>624</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>1041</v>
+        <v>1082</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I111" s="2">
         <v>1</v>
@@ -13645,28 +14149,28 @@
     </row>
     <row r="112" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>1042</v>
+        <v>1083</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>629</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>1043</v>
+        <v>1084</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I112" s="2">
         <v>1</v>
@@ -13674,28 +14178,28 @@
     </row>
     <row r="113" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>1044</v>
+        <v>1085</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>634</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>1045</v>
+        <v>1086</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I113" s="2">
         <v>1</v>
@@ -13703,28 +14207,28 @@
     </row>
     <row r="114" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>1046</v>
+        <v>1087</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>639</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>1047</v>
+        <v>1088</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I114" s="2">
         <v>1</v>
@@ -13732,28 +14236,28 @@
     </row>
     <row r="115" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>1048</v>
+        <v>1089</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>644</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>1049</v>
+        <v>1090</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I115" s="2">
         <v>1</v>
@@ -13761,28 +14265,28 @@
     </row>
     <row r="116" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>1050</v>
+        <v>1091</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>649</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>1051</v>
+        <v>1092</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I116" s="2">
         <v>1</v>
@@ -13790,28 +14294,28 @@
     </row>
     <row r="117" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>1052</v>
+        <v>1093</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>654</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>1053</v>
+        <v>1094</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I117" s="2">
         <v>1</v>
@@ -13819,28 +14323,28 @@
     </row>
     <row r="118" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>1054</v>
+        <v>1095</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>663</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>1055</v>
+        <v>1096</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>957</v>
+        <v>998</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I118" s="2">
         <v>1</v>
@@ -13848,28 +14352,28 @@
     </row>
     <row r="119" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>1056</v>
+        <v>1097</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>670</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>1055</v>
+        <v>1096</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>957</v>
+        <v>998</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I119" s="2">
         <v>1</v>
@@ -13877,28 +14381,28 @@
     </row>
     <row r="120" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>1057</v>
+        <v>1098</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>676</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>1058</v>
+        <v>1099</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I120" s="2">
         <v>1</v>
@@ -13906,28 +14410,28 @@
     </row>
     <row r="121" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>1059</v>
+        <v>1100</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>683</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>1060</v>
+        <v>1101</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I121" s="2">
         <v>1</v>
@@ -13935,28 +14439,28 @@
     </row>
     <row r="122" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>1061</v>
+        <v>1102</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>689</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>1060</v>
+        <v>1101</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I122" s="2">
         <v>1</v>
@@ -13964,28 +14468,28 @@
     </row>
     <row r="123" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>1062</v>
+        <v>1103</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>693</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>1060</v>
+        <v>1101</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I123" s="2">
         <v>1</v>
@@ -13993,28 +14497,28 @@
     </row>
     <row r="124" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>1063</v>
+        <v>1104</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>698</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>1064</v>
+        <v>1105</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1065</v>
+        <v>1106</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I124" s="2">
         <v>1</v>
@@ -14022,28 +14526,28 @@
     </row>
     <row r="125" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>1066</v>
+        <v>1107</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>706</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>1064</v>
+        <v>1105</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1067</v>
+        <v>1108</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>824</v>
+        <v>865</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1068</v>
+        <v>1109</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I125" s="2">
         <v>1</v>
@@ -14051,28 +14555,28 @@
     </row>
     <row r="126" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>1069</v>
+        <v>1110</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>712</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>1064</v>
+        <v>1105</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1070</v>
+        <v>1111</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>817</v>
+        <v>858</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>1071</v>
+        <v>1112</v>
       </c>
       <c r="I126" s="2">
         <v>2</v>
@@ -14080,28 +14584,28 @@
     </row>
     <row r="127" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>1072</v>
+        <v>1113</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>718</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>1064</v>
+        <v>1105</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1073</v>
+        <v>1114</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>817</v>
+        <v>858</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>1071</v>
+        <v>1112</v>
       </c>
       <c r="I127" s="2">
         <v>2</v>
@@ -14109,28 +14613,28 @@
     </row>
     <row r="128" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>1074</v>
+        <v>1115</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>724</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>1075</v>
+        <v>1116</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1076</v>
+        <v>1117</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I128" s="2">
         <v>1</v>
@@ -14138,28 +14642,28 @@
     </row>
     <row r="129" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>1077</v>
+        <v>1118</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>730</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>1075</v>
+        <v>1116</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1078</v>
+        <v>1119</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I129" s="2">
         <v>1</v>
@@ -14167,28 +14671,28 @@
     </row>
     <row r="130" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>1079</v>
+        <v>1120</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>736</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>1075</v>
+        <v>1116</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1080</v>
+        <v>1121</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I130" s="2">
         <v>1</v>
@@ -14196,28 +14700,28 @@
     </row>
     <row r="131" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>1081</v>
+        <v>1122</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>742</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>1075</v>
+        <v>1116</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1082</v>
+        <v>1123</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>817</v>
+        <v>858</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>824</v>
+        <v>865</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>1083</v>
+        <v>1124</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I131" s="2">
         <v>1</v>
@@ -14225,28 +14729,28 @@
     </row>
     <row r="132" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>1084</v>
+        <v>1125</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>748</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>1085</v>
+        <v>1126</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1086</v>
+        <v>1127</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I132" s="2">
         <v>1</v>
@@ -14254,28 +14758,28 @@
     </row>
     <row r="133" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>1087</v>
+        <v>1128</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>1085</v>
+        <v>1126</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1088</v>
+        <v>1129</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>824</v>
+        <v>865</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>1089</v>
+        <v>1130</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="I133" s="2">
         <v>1</v>
@@ -14283,28 +14787,28 @@
     </row>
     <row r="134" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>1090</v>
+        <v>1131</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>760</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>1091</v>
+        <v>1132</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>1092</v>
+        <v>1133</v>
       </c>
       <c r="I134" s="2">
         <v>1</v>
@@ -14312,28 +14816,28 @@
     </row>
     <row r="135" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>1093</v>
+        <v>1134</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>767</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>1094</v>
+        <v>1135</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>1092</v>
+        <v>1133</v>
       </c>
       <c r="I135" s="2">
         <v>1</v>
@@ -14341,28 +14845,28 @@
     </row>
     <row r="136" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>1095</v>
+        <v>1136</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>772</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>1096</v>
+        <v>1137</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>957</v>
+        <v>998</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>1092</v>
+        <v>1133</v>
       </c>
       <c r="I136" s="2">
         <v>1</v>
@@ -14370,28 +14874,28 @@
     </row>
     <row r="137" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>1097</v>
+        <v>1138</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>778</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>1096</v>
+        <v>1137</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1098</v>
+        <v>1139</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>817</v>
+        <v>858</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>1092</v>
+        <v>1133</v>
       </c>
       <c r="I137" s="2">
         <v>1</v>
@@ -14399,30 +14903,233 @@
     </row>
     <row r="138" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>1099</v>
+        <v>1140</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>784</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>1100</v>
+        <v>1141</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>957</v>
+        <v>998</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="F138" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I138" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I139" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I140" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="G138" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H138" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="I138" s="2">
+      <c r="C141" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I141" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I142" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I143" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I144" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I145" s="2">
         <v>1</v>
       </c>
     </row>
@@ -14443,18 +15150,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1101</v>
+        <v>1156</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1102</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1103</v>
+        <v>1158</v>
       </c>
       <c r="B2" t="s">
-        <v>1104</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -14462,55 +15169,55 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>1105</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1106</v>
+        <v>1161</v>
       </c>
       <c r="B4" t="s">
-        <v>1107</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1108</v>
+        <v>1163</v>
       </c>
       <c r="B5" t="s">
-        <v>1109</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1110</v>
+        <v>1165</v>
       </c>
       <c r="B6" t="s">
-        <v>1111</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1112</v>
+        <v>1167</v>
       </c>
       <c r="B7" t="s">
-        <v>1113</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1114</v>
+        <v>1169</v>
       </c>
       <c r="B8" t="s">
-        <v>1115</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1116</v>
+        <v>1171</v>
       </c>
       <c r="B9" t="s">
-        <v>1117</v>
+        <v>1172</v>
       </c>
     </row>
   </sheetData>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
@@ -2089,7 +2089,7 @@
     <t>functional, automation</t>
   </si>
   <si>
-    <t>AQPI-33, REQ-122, BR-122</t>
+    <t>AQPI-15, AQPI-33, REQ-122, BR-122</t>
   </si>
   <si>
     <t>Changed</t>
@@ -2121,7 +2121,7 @@
     <t>Revalidation requires acknowledgement; first submit HTTP 409 PRICE_CHANGE_REQUIRES_ACKNOWLEDGEMENT; after acknowledging HTTP 201</t>
   </si>
   <si>
-    <t>cart-service/src/main/resources/cart-service.yml, REQ-123, BR-123</t>
+    <t>AQPI-17, REQ-123, BR-123</t>
   </si>
   <si>
     <t>TC-F-114</t>
@@ -2160,7 +2160,7 @@
     <t>First 5 resends HTTP 202, the next HTTP 429; still one reservation</t>
   </si>
   <si>
-    <t>AQPI-35, REQ-124, BR-124</t>
+    <t>AQPI-26, AQPI-35, REQ-124, BR-124</t>
   </si>
   <si>
     <t>v2 (CYC-4): name was "The 4th resend within 24 hours is refused"; expected was "First 3 resends HTTP 202, the next HTTP 429; still one reservation"</t>
@@ -2182,7 +2182,7 @@
     <t>HTTP 400 IDEMPOTENCY_KEY_REQUIRED</t>
   </si>
   <si>
-    <t>reservation-service/src/main/resources/reservation-service.yml, REQ-125, BR-125</t>
+    <t>AQPI-21, REQ-125, BR-125</t>
   </si>
   <si>
     <t>TC-F-117</t>
@@ -2232,7 +2232,7 @@
     <t>HTTP 200 with a searchId</t>
   </si>
   <si>
-    <t>AQPI-34, REQ-126, BR-126</t>
+    <t>AQPI-4, AQPI-34, REQ-126, BR-126</t>
   </si>
   <si>
     <t>v2 (CYC-4): re-designed because a rule it depends on changed; case text unchanged</t>
@@ -2307,7 +2307,7 @@
     <t>occupancy.adults=4; every other booking attribute from the hotel data dictionary examples</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-127, BR-127</t>
+    <t>AQPI-4, REQ-127, BR-127</t>
   </si>
   <si>
     <t>TC-F-124</t>
@@ -2379,7 +2379,7 @@
     <t>stay.checkInOffsetDays=500; every other booking attribute from the hotel data dictionary examples</t>
   </si>
   <si>
-    <t>search-service/src/main/resources/search-service.yml, REQ-128, BR-128</t>
+    <t>AQPI-4, REQ-128, BR-128</t>
   </si>
   <si>
     <t>TC-F-128</t>
@@ -3635,7 +3635,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T19:44:35.503Z</t>
+    <t>2026-10-02T20:05:34.129Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
@@ -3635,7 +3635,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T20:05:34.129Z</t>
+    <t>2026-10-02T20:26:37.703Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/04-test-cases/CYC-4-test-cases.xlsx
@@ -2089,7 +2089,7 @@
     <t>functional, automation</t>
   </si>
   <si>
-    <t>AQPI-15, AQPI-33, REQ-122, BR-122</t>
+    <t>AQPI-33, REQ-122, BR-122</t>
   </si>
   <si>
     <t>Changed</t>
@@ -2160,7 +2160,7 @@
     <t>First 5 resends HTTP 202, the next HTTP 429; still one reservation</t>
   </si>
   <si>
-    <t>AQPI-26, AQPI-35, REQ-124, BR-124</t>
+    <t>AQPI-35, REQ-124, BR-124</t>
   </si>
   <si>
     <t>v2 (CYC-4): name was "The 4th resend within 24 hours is refused"; expected was "First 3 resends HTTP 202, the next HTTP 429; still one reservation"</t>
@@ -2232,7 +2232,7 @@
     <t>HTTP 200 with a searchId</t>
   </si>
   <si>
-    <t>AQPI-4, AQPI-34, REQ-126, BR-126</t>
+    <t>AQPI-34, REQ-126, BR-126</t>
   </si>
   <si>
     <t>v2 (CYC-4): re-designed because a rule it depends on changed; case text unchanged</t>
@@ -3635,7 +3635,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T20:26:37.703Z</t>
+    <t>2026-10-02T20:29:20.414Z</t>
   </si>
   <si>
     <t>Column order</t>
